--- a/test-files/продажи.xlsx
+++ b/test-files/продажи.xlsx
@@ -58,7 +58,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,15 +425,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,101 +470,145 @@
           <t>Телефон</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Возраст</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Бонус, %</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Попова Елена Александровна</t>
+          <t>Кузнецова Екатерина Игоревна</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Бухгалтер</t>
+          <t>UX-исследователь</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Поддержка</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>114986</v>
+        <v>136714</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09.07.2020</t>
+          <t>02.02.2023</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+71509839301</t>
-        </is>
+          <t>+74313518233</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>kuznetsova@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>59</v>
+      </c>
+      <c r="I2" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Петров Пётр Петрович</t>
+          <t>Лебедева Светлана Петровна</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Старший аналитик</t>
+          <t>Разработчик</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>58234</v>
+        <v>140220.27</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15.09.2021</t>
+          <t>28.12.2023</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+71834738299</t>
-        </is>
+          <t>+70084271094</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>lebedeva@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>33</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Соколова Наталья Андреевна</t>
+          <t>Кузнецова Екатерина Игоревна</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Старший аналитик</t>
+          <t>Старший менеджер</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>156708</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>19.02.2020</t>
-        </is>
-      </c>
+        <v>207361.43</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+71165667010</t>
-        </is>
+          <t>+79413186999</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>kuznetsova@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Сидорова Ольга Дмитриевна</t>
+          <t>Попова Елена Александровна</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -571,27 +618,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>115183</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>24.02.2020</t>
-        </is>
-      </c>
+        <v>290027.19</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+73872624731</t>
-        </is>
+          <t>+73412328120</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>popova@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>52</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Смирнова Татьяна Николаевна</t>
+          <t>Новиков Илья Романович</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -601,27 +655,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63261</v>
+        <v>230193</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24.01.2024</t>
+          <t>19.12.2020</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+70132677360</t>
-        </is>
+          <t>+79361832421</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>60</v>
+      </c>
+      <c r="I6" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Соколов Михаил Викторович</t>
+          <t>Новиков Илья Романович</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -631,122 +692,162 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>152346</v>
+        <v>155515</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.12.2020</t>
+          <t>12.08.2023</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+77468723430</t>
-        </is>
+          <t>+77190659401</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>novikov@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>58</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Козлова Юлия Романовна</t>
+          <t>Новикова Дарья Викторовна</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Тестировщик</t>
+          <t>HR-специалист</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>246077</v>
+        <v>95925</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08.07.2021</t>
+          <t>17.12.2022</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+70097882081</t>
-        </is>
+          <t>+72967175655</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>novikova@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>43</v>
+      </c>
+      <c r="I8" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Соколов Михаил Викторович</t>
+          <t>Новиков Илья Романович</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Старший менеджер</t>
+          <t>Финансовый аналитик</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Аналитика</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>67815</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>21.08.2020</t>
-        </is>
-      </c>
+        <v>169229</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+76193990916</t>
-        </is>
+          <t>+71680876038</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>novikov@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>62</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Козлова Юлия Романовна</t>
+          <t>Попов Андрей Дмитриевич</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Специалист по продажам</t>
+          <t>Разработчик</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Финансы</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>132934</v>
+        <v>233042</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>04.12.2020</t>
+          <t>29.04.2018</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+73534624751</t>
-        </is>
+          <t>+79324808613</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>popov@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>51</v>
+      </c>
+      <c r="I10" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Иванов Иван Иванович</t>
+          <t>Смирнов Владимир Андреевич</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Бухгалтер</t>
+          <t>Дизайнер</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -755,77 +856,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>197585</v>
+        <v>258680.99</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14.02.2019</t>
+          <t>25.09.2020</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+71838425135</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Новиков Илья Романович</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Аналитик</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Продажи</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>192401</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>24.05.2021</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>+79808412411</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Лебедева Светлана Петровна</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Аналитик</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Финансы</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>123860</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>13.10.2024</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>+73534874016</t>
-        </is>
+          <t>+72639821465</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>smirnov@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>22</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
